--- a/rtss-pre1917/charts/birth-death-counts/Бакинская с Баку.xlsx
+++ b/rtss-pre1917/charts/birth-death-counts/Бакинская с Баку.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22527"/>
+  <workbookPr/>
   <mc:AlternateContent>
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\github\RTSS\rtss-pre1917\src\main\resources\excel-templates\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\WINAPPS\SLOVO\UKR\github\RTSS\rtss-pre1917\src\main\resources\excel-templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02D646B5-30C0-4CCE-942B-EA2EDD51EDDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C22C6F2-85F9-4F80-9D40-5767A807E8EB}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="57480" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{552C350D-897F-4D5C-BE01-5853E10F71A5}"/>
+    <workbookView xWindow="-60" yWindow="-60" windowWidth="38520" windowHeight="23700" xr2:uid="{552C350D-897F-4D5C-BE01-5853E10F71A5}"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -26,9 +26,9 @@
         <xcalcf:feature name="microsoft.com:Single"/>
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
@@ -82,7 +82,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="0"/>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -143,15 +143,19 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -914,12 +918,12 @@
             <c:numRef>
               <c:f>data!$E$6:$E$40</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>#,##0</c:formatCode>
                 <c:ptCount val="35"/>
-                <c:pt idx="5" formatCode="#,##0">
+                <c:pt idx="5">
                   <c:v>1200</c:v>
                 </c:pt>
-                <c:pt idx="6" formatCode="#,##0">
+                <c:pt idx="6">
                   <c:v>1500</c:v>
                 </c:pt>
                 <c:pt idx="7">
@@ -1089,12 +1093,12 @@
             <c:numRef>
               <c:f>data!$F$6:$F$40</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>#,##0</c:formatCode>
                 <c:ptCount val="35"/>
-                <c:pt idx="5" formatCode="#,##0">
+                <c:pt idx="5">
                   <c:v>1350</c:v>
                 </c:pt>
-                <c:pt idx="6" formatCode="#,##0">
+                <c:pt idx="6">
                   <c:v>1200</c:v>
                 </c:pt>
               </c:numCache>
@@ -1175,7 +1179,7 @@
                 <a:cs typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="en-US"/>
+            <a:endParaRPr lang="ru-RU"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="689771312"/>
@@ -1237,7 +1241,7 @@
                 <a:cs typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="en-US"/>
+            <a:endParaRPr lang="ru-RU"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="694533552"/>
@@ -1279,13 +1283,12 @@
               <a:cs typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="en-US"/>
+          <a:endParaRPr lang="ru-RU"/>
         </a:p>
       </c:txPr>
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -1293,6 +1296,7 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
+    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -1316,7 +1320,7 @@
       <a:pPr>
         <a:defRPr/>
       </a:pPr>
-      <a:endParaRPr lang="en-US"/>
+      <a:endParaRPr lang="ru-RU"/>
     </a:p>
   </c:txPr>
   <c:printSettings>
@@ -2242,16 +2246,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5ADC5F70-B21E-4A44-9C44-374DD68BE283}">
   <dimension ref="A1:AD40"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="2" max="2" customWidth="true" width="11.3671875"/>
+    <col min="2" max="2" customWidth="true" width="11.375"/>
     <col min="3" max="3" customWidth="true" width="14.0"/>
-    <col min="4" max="4" customWidth="true" width="5.3671875"/>
-    <col min="5" max="5" customWidth="true" width="10.578125"/>
-    <col min="6" max="6" customWidth="true" width="10.5234375"/>
+    <col min="4" max="4" customWidth="true" width="5.375"/>
+    <col min="5" max="5" customWidth="true" width="10.625"/>
+    <col min="6" max="6" customWidth="true" width="10.5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" ht="20.399999999999999" x14ac:dyDescent="0.75">
+    <row r="1" spans="1:30" ht="21">
       <c r="A1" s="1" t="s">
         <v>11</v>
       </c>
@@ -2268,41 +2272,41 @@
       <c r="J1" s="2"/>
       <c r="K1" s="2"/>
     </row>
-    <row r="3" spans="1:30" ht="15.6" x14ac:dyDescent="0.6">
+    <row r="3" spans="1:30" ht="15.75">
       <c r="A3" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="8" t="s">
+      <c r="B3" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="8"/>
-      <c r="D3" s="5"/>
-      <c r="E3" s="8" t="s">
+      <c r="C3" s="5"/>
+      <c r="D3" s="6"/>
+      <c r="E3" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="F3" s="8"/>
-    </row>
-    <row r="4" spans="1:30" ht="15.6" x14ac:dyDescent="0.6">
-      <c r="A4" s="5"/>
-      <c r="B4" s="8" t="s">
+      <c r="F3" s="5"/>
+    </row>
+    <row r="4" spans="1:30" ht="15.75">
+      <c r="A4" s="6"/>
+      <c r="B4" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="8"/>
-      <c r="D4" s="5"/>
-      <c r="E4" s="8" t="s">
+      <c r="C4" s="5"/>
+      <c r="D4" s="6"/>
+      <c r="E4" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="8"/>
-    </row>
-    <row r="5" spans="1:30" ht="15.6" x14ac:dyDescent="0.6">
-      <c r="A5" s="5"/>
+      <c r="F4" s="5"/>
+    </row>
+    <row r="5" spans="1:30" ht="15.75">
+      <c r="A5" s="6"/>
       <c r="B5" s="4" t="s">
         <v>2</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="D5" s="5"/>
+      <c r="D5" s="6"/>
       <c r="E5" s="4" t="s">
         <v>6</v>
       </c>
@@ -2314,17 +2318,17 @@
       <c r="AC5" s="3"/>
       <c r="AD5" s="3"/>
     </row>
-    <row r="6" spans="1:30" ht="15.6" x14ac:dyDescent="0.6">
-      <c r="A6" s="6">
+    <row r="6" spans="1:30" ht="15.75">
+      <c r="A6" s="7">
         <v>1880</v>
       </c>
-      <c r="B6" s="7"/>
-      <c r="C6" s="7"/>
-      <c r="D6" s="5"/>
-      <c r="E6" s="5" t="s">
+      <c r="B6" s="8"/>
+      <c r="C6" s="8"/>
+      <c r="D6" s="8"/>
+      <c r="E6" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="F6" s="5" t="s">
+      <c r="F6" s="8" t="s">
         <v>8</v>
       </c>
       <c r="AA6" s="3"/>
@@ -2332,18 +2336,18 @@
       <c r="AC6" s="3"/>
       <c r="AD6" s="3"/>
     </row>
-    <row r="7" spans="1:30" ht="15.6" x14ac:dyDescent="0.6">
-      <c r="A7" s="6" t="n">
+    <row r="7" spans="1:30" ht="15.75">
+      <c r="A7" s="7" t="n">
         <f>A6+1</f>
         <v>1881.0</v>
       </c>
-      <c r="B7" s="7"/>
-      <c r="C7" s="7"/>
-      <c r="D7" s="5"/>
-      <c r="E7" s="5" t="s">
+      <c r="B7" s="8"/>
+      <c r="C7" s="8"/>
+      <c r="D7" s="8"/>
+      <c r="E7" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="F7" s="5" t="s">
+      <c r="F7" s="8" t="s">
         <v>8</v>
       </c>
       <c r="AA7" s="3"/>
@@ -2351,18 +2355,18 @@
       <c r="AC7" s="3"/>
       <c r="AD7" s="3"/>
     </row>
-    <row r="8" spans="1:30" ht="15.6" x14ac:dyDescent="0.6">
-      <c r="A8" s="6" t="n">
+    <row r="8" spans="1:30" ht="15.75">
+      <c r="A8" s="7" t="n">
         <f t="shared" ref="A8:A40" si="0">A7+1</f>
         <v>1882.0</v>
       </c>
-      <c r="B8" s="7"/>
-      <c r="C8" s="7"/>
-      <c r="D8" s="5"/>
-      <c r="E8" s="5" t="s">
+      <c r="B8" s="8"/>
+      <c r="C8" s="8"/>
+      <c r="D8" s="8"/>
+      <c r="E8" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="F8" s="5" t="s">
+      <c r="F8" s="8" t="s">
         <v>8</v>
       </c>
       <c r="AA8" s="3"/>
@@ -2370,18 +2374,18 @@
       <c r="AC8" s="3"/>
       <c r="AD8" s="3"/>
     </row>
-    <row r="9" spans="1:30" ht="15.6" x14ac:dyDescent="0.6">
-      <c r="A9" s="6" t="n">
+    <row r="9" spans="1:30" ht="15.75">
+      <c r="A9" s="7" t="n">
         <f t="shared" si="0"/>
         <v>1883.0</v>
       </c>
-      <c r="B9" s="7"/>
-      <c r="C9" s="7"/>
-      <c r="D9" s="5"/>
-      <c r="E9" s="5" t="s">
+      <c r="B9" s="8"/>
+      <c r="C9" s="8"/>
+      <c r="D9" s="8"/>
+      <c r="E9" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="F9" s="5" t="s">
+      <c r="F9" s="8" t="s">
         <v>8</v>
       </c>
       <c r="AA9" s="3"/>
@@ -2389,18 +2393,18 @@
       <c r="AC9" s="3"/>
       <c r="AD9" s="3"/>
     </row>
-    <row r="10" spans="1:30" ht="15.6" x14ac:dyDescent="0.6">
-      <c r="A10" s="6" t="n">
+    <row r="10" spans="1:30" ht="15.75">
+      <c r="A10" s="7" t="n">
         <f t="shared" si="0"/>
         <v>1884.0</v>
       </c>
-      <c r="B10" s="7"/>
-      <c r="C10" s="7"/>
-      <c r="D10" s="5"/>
-      <c r="E10" s="5" t="s">
+      <c r="B10" s="8"/>
+      <c r="C10" s="8"/>
+      <c r="D10" s="8"/>
+      <c r="E10" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="F10" s="5" t="s">
+      <c r="F10" s="8" t="s">
         <v>8</v>
       </c>
       <c r="AA10" s="3"/>
@@ -2408,18 +2412,18 @@
       <c r="AC10" s="3"/>
       <c r="AD10" s="3"/>
     </row>
-    <row r="11" spans="1:30" ht="15.6" x14ac:dyDescent="0.6">
-      <c r="A11" s="6" t="n">
+    <row r="11" spans="1:30" ht="15.75">
+      <c r="A11" s="7" t="n">
         <f t="shared" si="0"/>
         <v>1885.0</v>
       </c>
-      <c r="B11" s="7"/>
-      <c r="C11" s="7"/>
-      <c r="D11" s="5"/>
-      <c r="E11" s="7" t="s">
+      <c r="B11" s="8"/>
+      <c r="C11" s="8"/>
+      <c r="D11" s="8"/>
+      <c r="E11" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="F11" s="7" t="s">
+      <c r="F11" s="8" t="s">
         <v>8</v>
       </c>
       <c r="AA11" s="3"/>
@@ -2427,668 +2431,552 @@
       <c r="AC11" s="3"/>
       <c r="AD11" s="3"/>
     </row>
-    <row r="12" spans="1:30" ht="15.6" x14ac:dyDescent="0.6">
-      <c r="A12" s="6" t="n">
+    <row r="12" spans="1:30" ht="15.75">
+      <c r="A12" s="7" t="n">
         <f t="shared" si="0"/>
         <v>1886.0</v>
       </c>
-      <c r="B12" s="7" t="n">
+      <c r="B12" s="8" t="n">
         <v>20416.0</v>
       </c>
-      <c r="C12" s="7" t="n">
+      <c r="C12" s="8" t="n">
         <v>18215.0</v>
       </c>
-      <c r="D12" s="5"/>
-      <c r="E12" s="7" t="n">
-        <v>20416.0</v>
-      </c>
-      <c r="F12" s="7" t="n">
-        <v>18215.0</v>
-      </c>
+      <c r="D12" s="8"/>
+      <c r="E12" s="8"/>
+      <c r="F12" s="8"/>
       <c r="AA12" s="3"/>
       <c r="AB12" s="3"/>
       <c r="AC12" s="3"/>
       <c r="AD12" s="3"/>
     </row>
-    <row r="13" spans="1:30" ht="15.6" x14ac:dyDescent="0.6">
-      <c r="A13" s="6" t="n">
+    <row r="13" spans="1:30" ht="15.75">
+      <c r="A13" s="7" t="n">
         <f t="shared" si="0"/>
         <v>1887.0</v>
       </c>
-      <c r="B13" s="7" t="n">
+      <c r="B13" s="8" t="n">
         <v>17399.0</v>
       </c>
-      <c r="C13" s="7" t="n">
+      <c r="C13" s="8" t="n">
         <v>11940.0</v>
       </c>
-      <c r="D13" s="5"/>
-      <c r="E13" s="5" t="n">
-        <v>17399.0</v>
-      </c>
-      <c r="F13" s="5" t="n">
-        <v>11940.0</v>
-      </c>
+      <c r="D13" s="8"/>
+      <c r="E13" s="8"/>
+      <c r="F13" s="8"/>
       <c r="AA13" s="3"/>
       <c r="AB13" s="3"/>
       <c r="AC13" s="3"/>
       <c r="AD13" s="3"/>
     </row>
-    <row r="14" spans="1:30" ht="15.6" x14ac:dyDescent="0.6">
-      <c r="A14" s="6" t="n">
+    <row r="14" spans="1:30" ht="15.75">
+      <c r="A14" s="7" t="n">
         <f t="shared" si="0"/>
         <v>1888.0</v>
       </c>
-      <c r="B14" s="7" t="n">
+      <c r="B14" s="8" t="n">
         <v>19110.0</v>
       </c>
-      <c r="C14" s="7" t="n">
+      <c r="C14" s="8" t="n">
         <v>16636.0</v>
       </c>
-      <c r="D14" s="5"/>
-      <c r="E14" s="5" t="n">
-        <v>19110.0</v>
-      </c>
-      <c r="F14" s="5" t="n">
-        <v>16636.0</v>
-      </c>
+      <c r="D14" s="8"/>
+      <c r="E14" s="8"/>
+      <c r="F14" s="8"/>
       <c r="AA14" s="3"/>
       <c r="AB14" s="3"/>
       <c r="AC14" s="3"/>
       <c r="AD14" s="3"/>
     </row>
-    <row r="15" spans="1:30" ht="15.6" x14ac:dyDescent="0.6">
-      <c r="A15" s="6" t="n">
+    <row r="15" spans="1:30" ht="15.75">
+      <c r="A15" s="7" t="n">
         <f t="shared" si="0"/>
         <v>1889.0</v>
       </c>
-      <c r="B15" s="7" t="n">
+      <c r="B15" s="8" t="n">
         <v>16790.0</v>
       </c>
-      <c r="C15" s="7" t="n">
+      <c r="C15" s="8" t="n">
         <v>14838.0</v>
       </c>
-      <c r="D15" s="5"/>
-      <c r="E15" s="5" t="n">
-        <v>16790.0</v>
-      </c>
-      <c r="F15" s="5" t="n">
-        <v>14838.0</v>
-      </c>
+      <c r="D15" s="8"/>
+      <c r="E15" s="8"/>
+      <c r="F15" s="8"/>
       <c r="AA15" s="3"/>
       <c r="AB15" s="3"/>
       <c r="AC15" s="3"/>
       <c r="AD15" s="3"/>
     </row>
-    <row r="16" spans="1:30" ht="15.6" x14ac:dyDescent="0.6">
-      <c r="A16" s="6" t="n">
+    <row r="16" spans="1:30" ht="15.75">
+      <c r="A16" s="7" t="n">
         <f t="shared" si="0"/>
         <v>1890.0</v>
       </c>
-      <c r="B16" s="7" t="n">
+      <c r="B16" s="8" t="n">
         <v>22979.0</v>
       </c>
-      <c r="C16" s="7" t="n">
+      <c r="C16" s="8" t="n">
         <v>19460.0</v>
       </c>
-      <c r="D16" s="5"/>
-      <c r="E16" s="5" t="n">
-        <v>22979.0</v>
-      </c>
-      <c r="F16" s="5" t="n">
-        <v>19460.0</v>
-      </c>
+      <c r="D16" s="8"/>
+      <c r="E16" s="8"/>
+      <c r="F16" s="8"/>
       <c r="AA16" s="3"/>
       <c r="AB16" s="3"/>
       <c r="AC16" s="3"/>
       <c r="AD16" s="3"/>
     </row>
-    <row r="17" spans="1:30" ht="15.6" x14ac:dyDescent="0.6">
-      <c r="A17" s="6" t="n">
+    <row r="17" spans="1:30" ht="15.75">
+      <c r="A17" s="7" t="n">
         <f t="shared" si="0"/>
         <v>1891.0</v>
       </c>
-      <c r="B17" s="7" t="n">
+      <c r="B17" s="8" t="n">
         <v>21497.0</v>
       </c>
-      <c r="C17" s="7" t="n">
+      <c r="C17" s="8" t="n">
         <v>19879.0</v>
       </c>
-      <c r="D17" s="5"/>
-      <c r="E17" s="5" t="n">
-        <v>21497.0</v>
-      </c>
-      <c r="F17" s="5" t="n">
-        <v>19879.0</v>
-      </c>
+      <c r="D17" s="8"/>
+      <c r="E17" s="8"/>
+      <c r="F17" s="8"/>
       <c r="AA17" s="3"/>
       <c r="AB17" s="3"/>
       <c r="AC17" s="3"/>
       <c r="AD17" s="3"/>
     </row>
-    <row r="18" spans="1:30" ht="15.6" x14ac:dyDescent="0.6">
-      <c r="A18" s="6" t="n">
+    <row r="18" spans="1:30" ht="15.75">
+      <c r="A18" s="7" t="n">
         <f t="shared" si="0"/>
         <v>1892.0</v>
       </c>
-      <c r="B18" s="7" t="n">
+      <c r="B18" s="8" t="n">
         <v>15741.0</v>
       </c>
-      <c r="C18" s="7" t="n">
+      <c r="C18" s="8" t="n">
         <v>25201.0</v>
       </c>
-      <c r="D18" s="5"/>
-      <c r="E18" s="5" t="n">
-        <v>15741.0</v>
-      </c>
-      <c r="F18" s="5" t="n">
-        <v>25201.0</v>
-      </c>
+      <c r="D18" s="8"/>
+      <c r="E18" s="8"/>
+      <c r="F18" s="8"/>
       <c r="AA18" s="3"/>
       <c r="AB18" s="3"/>
       <c r="AC18" s="3"/>
       <c r="AD18" s="3"/>
     </row>
-    <row r="19" spans="1:30" ht="15.6" x14ac:dyDescent="0.6">
-      <c r="A19" s="6" t="n">
+    <row r="19" spans="1:30" ht="15.75">
+      <c r="A19" s="7" t="n">
         <f t="shared" si="0"/>
         <v>1893.0</v>
       </c>
-      <c r="B19" s="7" t="n">
+      <c r="B19" s="8" t="n">
         <v>14809.0</v>
       </c>
-      <c r="C19" s="7" t="n">
+      <c r="C19" s="8" t="n">
         <v>11510.0</v>
       </c>
-      <c r="D19" s="5"/>
-      <c r="E19" s="5" t="n">
-        <v>14809.0</v>
-      </c>
-      <c r="F19" s="5" t="n">
-        <v>11510.0</v>
-      </c>
+      <c r="D19" s="8"/>
+      <c r="E19" s="8"/>
+      <c r="F19" s="8"/>
       <c r="AA19" s="3"/>
       <c r="AB19" s="3"/>
       <c r="AC19" s="3"/>
       <c r="AD19" s="3"/>
     </row>
-    <row r="20" spans="1:30" ht="15.6" x14ac:dyDescent="0.6">
-      <c r="A20" s="6" t="n">
+    <row r="20" spans="1:30" ht="15.75">
+      <c r="A20" s="7" t="n">
         <f t="shared" si="0"/>
         <v>1894.0</v>
       </c>
-      <c r="B20" s="7" t="n">
+      <c r="B20" s="8" t="n">
         <v>20325.0</v>
       </c>
-      <c r="C20" s="7" t="n">
+      <c r="C20" s="8" t="n">
         <v>13920.0</v>
       </c>
-      <c r="D20" s="5"/>
-      <c r="E20" s="5" t="n">
-        <v>20325.0</v>
-      </c>
-      <c r="F20" s="5" t="n">
-        <v>13920.0</v>
-      </c>
+      <c r="D20" s="8"/>
+      <c r="E20" s="8"/>
+      <c r="F20" s="8"/>
       <c r="AA20" s="3"/>
       <c r="AB20" s="3"/>
       <c r="AC20" s="3"/>
       <c r="AD20" s="3"/>
     </row>
-    <row r="21" spans="1:30" ht="15.6" x14ac:dyDescent="0.6">
-      <c r="A21" s="6" t="n">
+    <row r="21" spans="1:30" ht="15.75">
+      <c r="A21" s="7" t="n">
         <f t="shared" si="0"/>
         <v>1895.0</v>
       </c>
-      <c r="B21" s="7" t="n">
+      <c r="B21" s="8" t="n">
         <v>17107.0</v>
       </c>
-      <c r="C21" s="7" t="n">
+      <c r="C21" s="8" t="n">
         <v>12644.0</v>
       </c>
-      <c r="D21" s="5"/>
-      <c r="E21" s="5" t="n">
-        <v>17107.0</v>
-      </c>
-      <c r="F21" s="5" t="n">
-        <v>12644.0</v>
-      </c>
+      <c r="D21" s="8"/>
+      <c r="E21" s="8"/>
+      <c r="F21" s="8"/>
       <c r="AA21" s="3"/>
       <c r="AB21" s="3"/>
       <c r="AC21" s="3"/>
       <c r="AD21" s="3"/>
     </row>
-    <row r="22" spans="1:30" ht="15.6" x14ac:dyDescent="0.6">
-      <c r="A22" s="6" t="n">
+    <row r="22" spans="1:30" ht="15.75">
+      <c r="A22" s="7" t="n">
         <f t="shared" si="0"/>
         <v>1896.0</v>
       </c>
-      <c r="B22" s="7" t="n">
+      <c r="B22" s="8" t="n">
         <v>18040.0</v>
       </c>
-      <c r="C22" s="7" t="n">
+      <c r="C22" s="8" t="n">
         <v>14331.0</v>
       </c>
-      <c r="D22" s="5"/>
-      <c r="E22" s="5" t="n">
-        <v>18040.0</v>
-      </c>
-      <c r="F22" s="5" t="n">
-        <v>14331.0</v>
-      </c>
+      <c r="D22" s="8"/>
+      <c r="E22" s="8"/>
+      <c r="F22" s="8"/>
       <c r="AA22" s="3"/>
       <c r="AB22" s="3"/>
       <c r="AC22" s="3"/>
       <c r="AD22" s="3"/>
     </row>
-    <row r="23" spans="1:30" ht="15.6" x14ac:dyDescent="0.6">
-      <c r="A23" s="6" t="n">
+    <row r="23" spans="1:30" ht="15.75">
+      <c r="A23" s="7" t="n">
         <f t="shared" si="0"/>
         <v>1897.0</v>
       </c>
-      <c r="B23" s="7" t="n">
+      <c r="B23" s="8" t="n">
         <v>20222.0</v>
       </c>
-      <c r="C23" s="7" t="n">
+      <c r="C23" s="8" t="n">
         <v>14622.0</v>
       </c>
-      <c r="D23" s="5"/>
-      <c r="E23" s="5" t="n">
-        <v>20222.0</v>
-      </c>
-      <c r="F23" s="5" t="n">
-        <v>14622.0</v>
-      </c>
+      <c r="D23" s="8"/>
+      <c r="E23" s="8"/>
+      <c r="F23" s="8"/>
       <c r="AA23" s="3"/>
       <c r="AB23" s="3"/>
       <c r="AC23" s="3"/>
       <c r="AD23" s="3"/>
     </row>
-    <row r="24" spans="1:30" ht="15.6" x14ac:dyDescent="0.6">
-      <c r="A24" s="6" t="n">
+    <row r="24" spans="1:30" ht="15.75">
+      <c r="A24" s="7" t="n">
         <f t="shared" si="0"/>
         <v>1898.0</v>
       </c>
-      <c r="B24" s="7" t="n">
+      <c r="B24" s="8" t="n">
         <v>20107.0</v>
       </c>
-      <c r="C24" s="7" t="n">
+      <c r="C24" s="8" t="n">
         <v>14435.0</v>
       </c>
-      <c r="D24" s="5"/>
-      <c r="E24" s="5" t="n">
-        <v>20107.0</v>
-      </c>
-      <c r="F24" s="5" t="n">
-        <v>14435.0</v>
-      </c>
+      <c r="D24" s="8"/>
+      <c r="E24" s="8"/>
+      <c r="F24" s="8"/>
       <c r="AA24" s="3"/>
       <c r="AB24" s="3"/>
       <c r="AC24" s="3"/>
       <c r="AD24" s="3"/>
     </row>
-    <row r="25" spans="1:30" ht="15.6" x14ac:dyDescent="0.6">
-      <c r="A25" s="6" t="n">
+    <row r="25" spans="1:30" ht="15.75">
+      <c r="A25" s="7" t="n">
         <f t="shared" si="0"/>
         <v>1899.0</v>
       </c>
-      <c r="B25" s="7" t="n">
+      <c r="B25" s="8" t="n">
         <v>24466.0</v>
       </c>
-      <c r="C25" s="7" t="n">
+      <c r="C25" s="8" t="n">
         <v>19372.0</v>
       </c>
-      <c r="D25" s="5"/>
-      <c r="E25" s="5" t="n">
-        <v>24466.0</v>
-      </c>
-      <c r="F25" s="5" t="n">
-        <v>19372.0</v>
-      </c>
+      <c r="D25" s="8"/>
+      <c r="E25" s="8"/>
+      <c r="F25" s="8"/>
       <c r="AA25" s="3"/>
       <c r="AB25" s="3"/>
       <c r="AC25" s="3"/>
       <c r="AD25" s="3"/>
     </row>
-    <row r="26" spans="1:30" ht="15.6" x14ac:dyDescent="0.6">
-      <c r="A26" s="6" t="n">
+    <row r="26" spans="1:30" ht="15.75">
+      <c r="A26" s="7" t="n">
         <f t="shared" si="0"/>
         <v>1900.0</v>
       </c>
-      <c r="B26" s="7" t="n">
+      <c r="B26" s="8" t="n">
         <v>28968.0</v>
       </c>
-      <c r="C26" s="7" t="n">
+      <c r="C26" s="8" t="n">
         <v>18186.0</v>
       </c>
-      <c r="D26" s="5"/>
-      <c r="E26" s="5" t="n">
-        <v>28968.0</v>
-      </c>
-      <c r="F26" s="5" t="n">
-        <v>18186.0</v>
-      </c>
+      <c r="D26" s="8"/>
+      <c r="E26" s="8"/>
+      <c r="F26" s="8"/>
       <c r="AA26" s="3"/>
       <c r="AB26" s="3"/>
       <c r="AC26" s="3"/>
       <c r="AD26" s="3"/>
     </row>
-    <row r="27" spans="1:30" ht="15.6" x14ac:dyDescent="0.6">
-      <c r="A27" s="6" t="n">
+    <row r="27" spans="1:30" ht="15.75">
+      <c r="A27" s="7" t="n">
         <f t="shared" si="0"/>
         <v>1901.0</v>
       </c>
-      <c r="B27" s="7" t="n">
+      <c r="B27" s="8" t="n">
         <v>28616.0</v>
       </c>
-      <c r="C27" s="7" t="n">
+      <c r="C27" s="8" t="n">
         <v>17527.0</v>
       </c>
-      <c r="D27" s="5"/>
-      <c r="E27" s="5" t="n">
-        <v>28616.0</v>
-      </c>
-      <c r="F27" s="5" t="n">
-        <v>17527.0</v>
-      </c>
+      <c r="D27" s="8"/>
+      <c r="E27" s="8"/>
+      <c r="F27" s="8"/>
       <c r="AA27" s="3"/>
       <c r="AB27" s="3"/>
       <c r="AC27" s="3"/>
       <c r="AD27" s="3"/>
     </row>
-    <row r="28" spans="1:30" ht="15.6" x14ac:dyDescent="0.6">
-      <c r="A28" s="6" t="n">
+    <row r="28" spans="1:30" ht="15.75">
+      <c r="A28" s="7" t="n">
         <f t="shared" si="0"/>
         <v>1902.0</v>
       </c>
-      <c r="B28" s="7" t="n">
+      <c r="B28" s="8" t="n">
         <v>25656.0</v>
       </c>
-      <c r="C28" s="7" t="n">
+      <c r="C28" s="8" t="n">
         <v>18960.0</v>
       </c>
-      <c r="D28" s="5"/>
-      <c r="E28" s="5" t="n">
-        <v>25656.0</v>
-      </c>
-      <c r="F28" s="5" t="n">
-        <v>18960.0</v>
-      </c>
+      <c r="D28" s="8"/>
+      <c r="E28" s="8"/>
+      <c r="F28" s="8"/>
       <c r="AA28" s="3"/>
       <c r="AB28" s="3"/>
       <c r="AC28" s="3"/>
       <c r="AD28" s="3"/>
     </row>
-    <row r="29" spans="1:30" ht="15.6" x14ac:dyDescent="0.6">
-      <c r="A29" s="6" t="n">
+    <row r="29" spans="1:30" ht="15.75">
+      <c r="A29" s="7" t="n">
         <f t="shared" si="0"/>
         <v>1903.0</v>
       </c>
-      <c r="B29" s="7" t="n">
+      <c r="B29" s="8" t="n">
         <v>28650.0</v>
       </c>
-      <c r="C29" s="7" t="n">
+      <c r="C29" s="8" t="n">
         <v>14972.0</v>
       </c>
-      <c r="D29" s="5"/>
-      <c r="E29" s="5" t="n">
-        <v>28650.0</v>
-      </c>
-      <c r="F29" s="5" t="n">
-        <v>14972.0</v>
-      </c>
+      <c r="D29" s="8"/>
+      <c r="E29" s="8"/>
+      <c r="F29" s="8"/>
       <c r="AA29" s="3"/>
       <c r="AB29" s="3"/>
       <c r="AC29" s="3"/>
       <c r="AD29" s="3"/>
     </row>
-    <row r="30" spans="1:30" ht="15.6" x14ac:dyDescent="0.6">
-      <c r="A30" s="6" t="n">
+    <row r="30" spans="1:30" ht="15.75">
+      <c r="A30" s="7" t="n">
         <f t="shared" si="0"/>
         <v>1904.0</v>
       </c>
-      <c r="B30" s="7" t="n">
+      <c r="B30" s="8" t="n">
         <v>26831.0</v>
       </c>
-      <c r="C30" s="7" t="n">
+      <c r="C30" s="8" t="n">
         <v>17991.0</v>
       </c>
-      <c r="D30" s="5"/>
-      <c r="E30" s="5" t="n">
-        <v>26831.0</v>
-      </c>
-      <c r="F30" s="5" t="n">
-        <v>17991.0</v>
-      </c>
+      <c r="D30" s="8"/>
+      <c r="E30" s="8"/>
+      <c r="F30" s="8"/>
       <c r="AA30" s="3"/>
       <c r="AB30" s="3"/>
       <c r="AC30" s="3"/>
       <c r="AD30" s="3"/>
     </row>
-    <row r="31" spans="1:30" ht="15.6" x14ac:dyDescent="0.6">
-      <c r="A31" s="6" t="n">
+    <row r="31" spans="1:30" ht="15.75">
+      <c r="A31" s="7" t="n">
         <f t="shared" si="0"/>
         <v>1905.0</v>
       </c>
-      <c r="B31" s="7" t="n">
+      <c r="B31" s="8" t="n">
         <v>30426.0</v>
       </c>
-      <c r="C31" s="7" t="n">
+      <c r="C31" s="8" t="n">
         <v>21661.0</v>
       </c>
-      <c r="D31" s="5"/>
-      <c r="E31" s="5" t="n">
-        <v>30426.0</v>
-      </c>
-      <c r="F31" s="5" t="n">
-        <v>21661.0</v>
-      </c>
+      <c r="D31" s="8"/>
+      <c r="E31" s="8"/>
+      <c r="F31" s="8"/>
       <c r="AA31" s="3"/>
       <c r="AB31" s="3"/>
       <c r="AC31" s="3"/>
       <c r="AD31" s="3"/>
     </row>
-    <row r="32" spans="1:30" ht="15.6" x14ac:dyDescent="0.6">
-      <c r="A32" s="6" t="n">
+    <row r="32" spans="1:30" ht="15.75">
+      <c r="A32" s="7" t="n">
         <f t="shared" si="0"/>
         <v>1906.0</v>
       </c>
-      <c r="B32" s="7" t="n">
+      <c r="B32" s="8" t="n">
         <v>22668.0</v>
       </c>
-      <c r="C32" s="7" t="n">
+      <c r="C32" s="8" t="n">
         <v>18832.0</v>
       </c>
-      <c r="D32" s="5"/>
-      <c r="E32" s="5" t="n">
-        <v>22668.0</v>
-      </c>
-      <c r="F32" s="5" t="n">
-        <v>18832.0</v>
-      </c>
+      <c r="D32" s="8"/>
+      <c r="E32" s="8"/>
+      <c r="F32" s="8"/>
       <c r="AA32" s="3"/>
       <c r="AB32" s="3"/>
       <c r="AC32" s="3"/>
       <c r="AD32" s="3"/>
     </row>
-    <row r="33" spans="1:30" ht="15.6" x14ac:dyDescent="0.6">
-      <c r="A33" s="6" t="n">
+    <row r="33" spans="1:30" ht="15.75">
+      <c r="A33" s="7" t="n">
         <f t="shared" si="0"/>
         <v>1907.0</v>
       </c>
-      <c r="B33" s="7" t="n">
+      <c r="B33" s="8" t="n">
         <v>26891.0</v>
       </c>
-      <c r="C33" s="7" t="n">
+      <c r="C33" s="8" t="n">
         <v>19453.0</v>
       </c>
-      <c r="D33" s="5"/>
-      <c r="E33" s="5" t="n">
-        <v>26891.0</v>
-      </c>
-      <c r="F33" s="5" t="n">
-        <v>19453.0</v>
-      </c>
+      <c r="D33" s="8"/>
+      <c r="E33" s="8"/>
+      <c r="F33" s="8"/>
       <c r="AA33" s="3"/>
       <c r="AB33" s="3"/>
       <c r="AC33" s="3"/>
       <c r="AD33" s="3"/>
     </row>
-    <row r="34" spans="1:30" ht="15.6" x14ac:dyDescent="0.6">
-      <c r="A34" s="6" t="n">
+    <row r="34" spans="1:30" ht="15.75">
+      <c r="A34" s="7" t="n">
         <f t="shared" si="0"/>
         <v>1908.0</v>
       </c>
-      <c r="B34" s="7" t="n">
+      <c r="B34" s="8" t="n">
         <v>30026.0</v>
       </c>
-      <c r="C34" s="7" t="n">
+      <c r="C34" s="8" t="n">
         <v>21820.0</v>
       </c>
-      <c r="D34" s="5"/>
-      <c r="E34" s="5" t="n">
-        <v>30026.0</v>
-      </c>
-      <c r="F34" s="5" t="n">
-        <v>21820.0</v>
-      </c>
+      <c r="D34" s="8"/>
+      <c r="E34" s="8"/>
+      <c r="F34" s="8"/>
       <c r="AA34" s="3"/>
       <c r="AB34" s="3"/>
       <c r="AC34" s="3"/>
       <c r="AD34" s="3"/>
     </row>
-    <row r="35" spans="1:30" ht="15.6" x14ac:dyDescent="0.6">
-      <c r="A35" s="6" t="n">
+    <row r="35" spans="1:30" ht="15.75">
+      <c r="A35" s="7" t="n">
         <f t="shared" si="0"/>
         <v>1909.0</v>
       </c>
-      <c r="B35" s="7" t="n">
+      <c r="B35" s="8" t="n">
         <v>27604.0</v>
       </c>
-      <c r="C35" s="7" t="n">
+      <c r="C35" s="8" t="n">
         <v>19817.0</v>
       </c>
-      <c r="D35" s="5"/>
-      <c r="E35" s="5" t="n">
-        <v>27604.0</v>
-      </c>
-      <c r="F35" s="5" t="n">
-        <v>19817.0</v>
-      </c>
+      <c r="D35" s="8"/>
+      <c r="E35" s="8"/>
+      <c r="F35" s="8"/>
       <c r="AA35" s="3"/>
       <c r="AB35" s="3"/>
       <c r="AC35" s="3"/>
       <c r="AD35" s="3"/>
     </row>
-    <row r="36" spans="1:30" ht="15.6" x14ac:dyDescent="0.6">
-      <c r="A36" s="6" t="n">
+    <row r="36" spans="1:30" ht="15.75">
+      <c r="A36" s="7" t="n">
         <f t="shared" si="0"/>
         <v>1910.0</v>
       </c>
-      <c r="B36" s="7" t="n">
+      <c r="B36" s="8" t="n">
         <v>26210.0</v>
       </c>
-      <c r="C36" s="7" t="n">
+      <c r="C36" s="8" t="n">
         <v>22314.0</v>
       </c>
-      <c r="D36" s="5"/>
-      <c r="E36" s="5" t="n">
-        <v>26210.0</v>
-      </c>
-      <c r="F36" s="5" t="n">
-        <v>22314.0</v>
-      </c>
+      <c r="D36" s="8"/>
+      <c r="E36" s="8"/>
+      <c r="F36" s="8"/>
       <c r="AA36" s="3"/>
       <c r="AB36" s="3"/>
       <c r="AC36" s="3"/>
       <c r="AD36" s="3"/>
     </row>
-    <row r="37" spans="1:30" ht="15.6" x14ac:dyDescent="0.6">
-      <c r="A37" s="6" t="n">
+    <row r="37" spans="1:30" ht="15.75">
+      <c r="A37" s="7" t="n">
         <f t="shared" si="0"/>
         <v>1911.0</v>
       </c>
-      <c r="B37" s="7" t="n">
+      <c r="B37" s="8" t="n">
         <v>31120.0</v>
       </c>
-      <c r="C37" s="7" t="n">
+      <c r="C37" s="8" t="n">
         <v>21009.0</v>
       </c>
-      <c r="D37" s="5"/>
-      <c r="E37" s="5" t="n">
-        <v>31120.0</v>
-      </c>
-      <c r="F37" s="5" t="n">
-        <v>21009.0</v>
-      </c>
+      <c r="D37" s="8"/>
+      <c r="E37" s="8"/>
+      <c r="F37" s="8"/>
       <c r="AA37" s="3"/>
       <c r="AB37" s="3"/>
       <c r="AC37" s="3"/>
       <c r="AD37" s="3"/>
     </row>
-    <row r="38" spans="1:30" ht="15.6" x14ac:dyDescent="0.6">
-      <c r="A38" s="6" t="n">
+    <row r="38" spans="1:30" ht="15.75">
+      <c r="A38" s="7" t="n">
         <f t="shared" si="0"/>
         <v>1912.0</v>
       </c>
-      <c r="B38" s="7" t="n">
+      <c r="B38" s="8" t="n">
         <v>29548.0</v>
       </c>
-      <c r="C38" s="7" t="n">
+      <c r="C38" s="8" t="n">
         <v>20695.0</v>
       </c>
-      <c r="D38" s="5"/>
-      <c r="E38" s="5" t="n">
-        <v>29548.0</v>
-      </c>
-      <c r="F38" s="5" t="n">
-        <v>20695.0</v>
-      </c>
+      <c r="D38" s="8"/>
+      <c r="E38" s="8"/>
+      <c r="F38" s="8"/>
       <c r="AA38" s="3"/>
       <c r="AB38" s="3"/>
       <c r="AC38" s="3"/>
       <c r="AD38" s="3"/>
     </row>
-    <row r="39" spans="1:30" ht="15.6" x14ac:dyDescent="0.6">
-      <c r="A39" s="6" t="n">
+    <row r="39" spans="1:30" ht="15.75">
+      <c r="A39" s="7" t="n">
         <f t="shared" si="0"/>
         <v>1913.0</v>
       </c>
-      <c r="B39" s="7" t="n">
+      <c r="B39" s="8" t="n">
         <v>32898.0</v>
       </c>
-      <c r="C39" s="7" t="n">
+      <c r="C39" s="8" t="n">
         <v>20421.0</v>
       </c>
-      <c r="D39" s="5"/>
-      <c r="E39" s="5" t="n">
-        <v>32898.0</v>
-      </c>
-      <c r="F39" s="5" t="n">
-        <v>20421.0</v>
-      </c>
+      <c r="D39" s="8"/>
+      <c r="E39" s="8"/>
+      <c r="F39" s="8"/>
       <c r="AA39" s="3"/>
       <c r="AB39" s="3"/>
       <c r="AC39" s="3"/>
       <c r="AD39" s="3"/>
     </row>
-    <row r="40" spans="1:30" ht="15.6" x14ac:dyDescent="0.6">
-      <c r="A40" s="6" t="n">
+    <row r="40" spans="1:30" ht="15.75">
+      <c r="A40" s="7" t="n">
         <f t="shared" si="0"/>
         <v>1914.0</v>
       </c>
-      <c r="B40" s="7" t="n">
+      <c r="B40" s="8" t="n">
         <v>31703.0</v>
       </c>
-      <c r="C40" s="7" t="n">
+      <c r="C40" s="8" t="n">
         <v>22463.0</v>
       </c>
-      <c r="D40" s="5"/>
-      <c r="E40" s="5" t="n">
-        <v>31703.0</v>
-      </c>
-      <c r="F40" s="5" t="n">
-        <v>22463.0</v>
-      </c>
+      <c r="D40" s="8"/>
+      <c r="E40" s="8"/>
+      <c r="F40" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -3098,7 +2986,8 @@
     <mergeCell ref="E3:F3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 

--- a/rtss-pre1917/charts/birth-death-counts/Бакинская с Баку.xlsx
+++ b/rtss-pre1917/charts/birth-death-counts/Бакинская с Баку.xlsx
@@ -2257,14 +2257,14 @@
   <sheetData>
     <row r="1" spans="1:30" ht="21">
       <c r="A1" s="1" t="s">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
       <c r="F1" s="1" t="s">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="G1" s="2"/>
       <c r="H1" s="2"/>
